--- a/huge数据对比/3mz-vs-wgmy.xlsx
+++ b/huge数据对比/3mz-vs-wgmy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\huge数据对比\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EF991F-E37D-476B-8151-41EDABE0A712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAF0B74-C56A-4BB8-A1F3-1457DE747D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
